--- a/stories/arbres/ATOM-SAN.ECR.001-09.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-09.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Florian est dans sa chambre. Il regarde un petit écran. Des oiseaux passent. Papa s'assoit près du tapis. Papa dit : fini. L'adulte dit fini. Florian écoute. Parce que papa a dit fini, Florian va éteindre. Florian éteint l'écran. L'écran devient noir. Il pose la tablette. Papa dit : on prend un autre jeu. Florian va choisir un jeu. Il choisit le train en bois. Les roues sont lisses. Ils font un rail. Le train glisse. Florian dit : l'écran est éteint. Un autre jeu, c'est bien. Papa tape dans ses mains. Florian rit. Ils ajoutent un pont. Puis ils rangent les rails. Florian a su éteindre. Il a choisi un autre jeu.</t>
+          <t>Florian est dans sa chambre. Il regarde un petit écran. Des oiseaux passent. Papa s'assoit près du tapis. Fini. L'adulte dit fini. Florian écoute. Parce que papa a dit fini, Florian va éteindre. Florian éteint l'écran. L'écran devient noir. Il pose la tablette. On prend un autre jeu. Florian va choisir un jeu. Il choisit le train en bois. Les roues sont lisses. Ils font un rail. Le train glisse. L'écran est éteint. Un autre jeu, c'est bien. Papa tape dans ses mains. Florian rit. Ils ajoutent un pont. Puis ils rangent les rails. Florian a su éteindre. Il a choisi un autre jeu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Florian est dans sa chambre. Il regarde un petit écran. Des oiseaux passent. Papa s'assoit près du tapis.
+papa|Fini. L'adulte dit fini.
+narrateur|Florian écoute. Parce que papa a dit fini, Florian va éteindre. Florian éteint l'écran. L'écran devient noir. Il pose la tablette.
+papa|On prend un autre jeu.
+narrateur|Florian va choisir un jeu. Il choisit le train en bois. Les roues sont lisses. Ils font un rail. Le train glisse.
+enfant-m|L'écran est éteint.
+narrateur|Un autre jeu, c'est bien. Papa tape dans ses mains. Florian rit. Ils ajoutent un pont. Puis ils rangent les rails. Florian a su éteindre. Il a choisi un autre jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Papa dit fini. Que fait Florian ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Papa a dit fini. Florian a éteint. Il a pris un autre jeu. Le train en bois, c'était bien.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1828,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Le train reste sur le pont. Florian dit merci à papa. La chambre est calme.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1995,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ECR.001-09.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-09.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,11 @@
 narrateur|Un autre jeu, c'est bien. Papa tape dans ses mains. Florian rit. Ils ajoutent un pont. Puis ils rangent les rails. Florian a su éteindre. Il a choisi un autre jeu.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1509,7 @@
           <t>narrateur|Papa dit fini. Que fait Florian ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1681,7 @@
           <t>narrateur|Papa a dit fini. Florian a éteint. Il a pris un autre jeu. Le train en bois, c'était bien.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1845,7 @@
           <t>narrateur|Le train reste sur le pont. Florian dit merci à papa. La chambre est calme.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.ECR.001-09.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-09.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Florian éteint et prend le train en bois</t>
+          <t>Le train en bois</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une lampe orange veille. Papa dit fini. Raphaël éteint. Le train glisse sur le pont.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Florian est dans sa chambre. Il regarde un petit écran. Des oiseaux passent. Papa s'assoit près du tapis. Fini. L'adulte dit fini. Florian écoute. Parce que papa a dit fini, Florian va éteindre. Florian éteint l'écran. L'écran devient noir. Il pose la tablette. On prend un autre jeu. Florian va choisir un jeu. Il choisit le train en bois. Les roues sont lisses. Ils font un rail. Le train glisse. L'écran est éteint. Un autre jeu, c'est bien. Papa tape dans ses mains. Florian rit. Ils ajoutent un pont. Puis ils rangent les rails. Florian a su éteindre. Il a choisi un autre jeu.</t>
+          <t>Une petite lampe orange veille. Elle est près du lit. Le plancher de bois craque un peu. Un doudou attend sur l'oreiller. Une boîte de train est dans le coin. Ça sent le bois et le linge. Un rail dépasse déjà de la boîte. La fenêtre est un peu embuée. Raphaël, je m'assois ici. Tu vois la lampe ? Oui, papa. Elle est orange. En ce moment, Raphaël tient la tablette. Des oiseaux passent sur l'écran. Leurs ailes sont bleues. Les oiseaux, papa. Oui. Ils passent. Papa s'assoit près du tapis. Le tapis est un peu rêche. Fini. L'adulte dit fini. Raphaël écoute. C'est fini. On va éteindre. Raphaël va éteindre. Raphaël éteint l'écran. L'écran devient noir. Il pose la tablette. Bravo, Raphaël. Tu as éteint. On prend un autre jeu. Un autre jeu. Tu choisis ? Raphaël choisit le train en bois. Les roues sont lisses. Ils font un rail. Le bois claque un peu. Le train glisse. Il glisse. Oui. Tout doucement. On ajoute un wagon ? Raphaël pose un wagon rouge. Le wagon fait clic. Clic. Bravo. Ils ajoutent un pont. Le pont est petit et jaune. Le train passe dessous. Sous le pont. Oui. Sous le pont. Bravo. Tu as fait du bon travail. L'écran est éteint. Oui. Un autre jeu, c'est bien. Papa tape dans ses mains. Raphaël rit. La lampe orange veille encore.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,18 +1324,72 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Florian est dans sa chambre. Il regarde un petit écran. Des oiseaux passent. Papa s'assoit près du tapis.
-papa|Fini. L'adulte dit fini.
-narrateur|Florian écoute. Parce que papa a dit fini, Florian va éteindre. Florian éteint l'écran. L'écran devient noir. Il pose la tablette.
+          <t>narrateur|Une petite lampe orange veille.
+narrateur|Elle est près du lit.
+narrateur|Le plancher de bois craque un peu.
+narrateur|Un doudou attend sur l'oreiller.
+narrateur|Une boîte de train est dans le coin.
+narrateur|Ça sent le bois et le linge.
+narrateur|Un rail dépasse déjà de la boîte.
+narrateur|La fenêtre est un peu embuée.
+papa|Raphaël, je m'assois ici.
+papa|Tu vois la lampe ?
+enfant-m|Oui, papa.
+enfant-m|Elle est orange.
+narrateur|En ce moment, Raphaël tient la tablette.
+narrateur|Des oiseaux passent sur l'écran.
+narrateur|Leurs ailes sont bleues.
+enfant-m|Les oiseaux, papa.
+papa|Oui.
+papa|Ils passent.
+narrateur|Papa s'assoit près du tapis.
+narrateur|Le tapis est un peu rêche.
+papa|Fini.
+narrateur|L'adulte dit fini.
+narrateur|Raphaël écoute.
+enfant-m|C'est fini.
+papa|On va éteindre.
+narrateur|Raphaël va éteindre.
+narrateur|Raphaël éteint l'écran.
+narrateur|L'écran devient noir.
+narrateur|Il pose la tablette.
+papa|Bravo, Raphaël.
+papa|Tu as éteint.
 papa|On prend un autre jeu.
-narrateur|Florian va choisir un jeu. Il choisit le train en bois. Les roues sont lisses. Ils font un rail. Le train glisse.
+enfant-m|Un autre jeu.
+papa|Tu choisis ?
+narrateur|Raphaël choisit le train en bois.
+narrateur|Les roues sont lisses.
+narrateur|Ils font un rail.
+narrateur|Le bois claque un peu.
+narrateur|Le train glisse.
+enfant-m|Il glisse.
+papa|Oui.
+papa|Tout doucement.
+papa|On ajoute un wagon ?
+narrateur|Raphaël pose un wagon rouge.
+narrateur|Le wagon fait clic.
+enfant-m|Clic.
+papa|Bravo.
+narrateur|Ils ajoutent un pont.
+narrateur|Le pont est petit et jaune.
+narrateur|Le train passe dessous.
+enfant-m|Sous le pont.
+papa|Oui.
+papa|Sous le pont.
+papa|Bravo.
+papa|Tu as fait du bon travail.
 enfant-m|L'écran est éteint.
-narrateur|Un autre jeu, c'est bien. Papa tape dans ses mains. Florian rit. Ils ajoutent un pont. Puis ils rangent les rails. Florian a su éteindre. Il a choisi un autre jeu.</t>
+papa|Oui.
+papa|Un autre jeu, c'est bien.
+narrateur|Papa tape dans ses mains.
+narrateur|Raphaël rit.
+narrateur|La lampe orange veille encore.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>train_bois</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1416,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Papa dit fini. Que fait Florian ?</t>
+          <t>Papa dit fini. Que fait Raphaël ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1506,7 +1572,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Papa dit fini. Que fait Florian ?</t>
+          <t>narrateur|Papa dit fini.
+narrateur|Que fait Raphaël ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1534,7 +1601,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Papa a dit fini. Florian a éteint. Il a pris un autre jeu. Le train en bois, c'était bien.</t>
+          <t>Papa a dit fini. L'adulte a dit fini. Raphaël a éteint. Il a pris un autre jeu. Tu as éteint l'écran ? Oui, papa. Et après ? Un autre jeu. Bravo. Le train en bois, c'était bien. Raphaël touche une roue. La roue est lisse. Le wagon est encore dessus ? Oui, papa. Le pont jaune reste en place. La lampe veille encore.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1678,7 +1745,22 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Papa a dit fini. Florian a éteint. Il a pris un autre jeu. Le train en bois, c'était bien.</t>
+          <t>narrateur|Papa a dit fini.
+narrateur|L'adulte a dit fini.
+narrateur|Raphaël a éteint.
+narrateur|Il a pris un autre jeu.
+papa|Tu as éteint l'écran ?
+enfant-m|Oui, papa.
+papa|Et après ?
+enfant-m|Un autre jeu.
+papa|Bravo.
+papa|Le train en bois, c'était bien.
+narrateur|Raphaël touche une roue.
+narrateur|La roue est lisse.
+papa|Le wagon est encore dessus ?
+enfant-m|Oui, papa.
+narrateur|Le pont jaune reste en place.
+narrateur|La lampe veille encore.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1706,7 +1788,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Le train reste sur le pont. Florian dit merci à papa. La chambre est calme.</t>
+          <t>Le train reste sur le pont. On range les rails ? Ils rangent les rails. Le bois claque, tout doucement. Tu as fini de ranger ? Oui, papa. Bravo. Merci, papa. Merci, Raphaël. On pose le doudou ? Raphaël pose le doudou. Le doudou attend encore. La chambre est calme.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1842,7 +1924,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Le train reste sur le pont. Florian dit merci à papa. La chambre est calme.</t>
+          <t>narrateur|Le train reste sur le pont.
+papa|On range les rails ?
+narrateur|Ils rangent les rails.
+narrateur|Le bois claque, tout doucement.
+papa|Tu as fini de ranger ?
+enfant-m|Oui, papa.
+papa|Bravo.
+enfant-m|Merci, papa.
+papa|Merci, Raphaël.
+papa|On pose le doudou ?
+narrateur|Raphaël pose le doudou.
+narrateur|Le doudou attend encore.
+narrateur|La chambre est calme.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1870,7 +1964,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le train reste sur le pont. L'écran est éteint. Oui. Bravo, Raphaël. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2010,7 +2104,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le train reste sur le pont.
+enfant-m|L'écran est éteint.
+papa|Oui.
+papa|Bravo, Raphaël.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2032,7 +2130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2168,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ECR.001-09.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-09.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une petite lampe orange veille. Elle est près du lit. Le plancher de bois craque un peu. Un doudou attend sur l'oreiller. Une boîte de train est dans le coin. Ça sent le bois et le linge. Un rail dépasse déjà de la boîte. La fenêtre est un peu embuée. Raphaël, je m'assois ici. Tu vois la lampe ? Oui, papa. Elle est orange. En ce moment, Raphaël tient la tablette. Des oiseaux passent sur l'écran. Leurs ailes sont bleues. Les oiseaux, papa. Oui. Ils passent. Papa s'assoit près du tapis. Le tapis est un peu rêche. Fini. L'adulte dit fini. Raphaël écoute. C'est fini. On va éteindre. Raphaël va éteindre. Raphaël éteint l'écran. L'écran devient noir. Il pose la tablette. Bravo, Raphaël. Tu as éteint. On prend un autre jeu. Un autre jeu. Tu choisis ? Raphaël choisit le train en bois. Les roues sont lisses. Ils font un rail. Le bois claque un peu. Le train glisse. Il glisse. Oui. Tout doucement. On ajoute un wagon ? Raphaël pose un wagon rouge. Le wagon fait clic. Clic. Bravo. Ils ajoutent un pont. Le pont est petit et jaune. Le train passe dessous. Sous le pont. Oui. Sous le pont. Bravo. Tu as fait du bon travail. L'écran est éteint. Oui. Un autre jeu, c'est bien. Papa tape dans ses mains. Raphaël rit. La lampe orange veille encore.</t>
+          <t>Une petite lampe orange veille. Elle est près du lit. Le plancher de bois craque un peu. Un doudou attend sur l'oreiller. Une boîte de train est dans le coin. Ça sent le bois et le linge. Un rail dépasse déjà de la boîte. La fenêtre est un peu embuée. Raphaël, je m'assois ici. Tu vois la lampe ? Oui, papa. Elle est orange. En ce moment, Raphaël tient la tablette. Des oiseaux passent sur l'écran. Leurs ailes sont bleues. Les oiseaux, papa. Oui. Ils passent. Papa s'assoit près du tapis. Le tapis est un peu rêche. Fini. L'adulte dit fini. Raphaël écoute. C'est fini. On va éteindre. Raphaël va éteindre. Raphaël éteint l'écran. L'écran devient noir. Il pose la tablette. Bravo, Raphaël. Tu as éteint. On prend un autre jeu. Un autre jeu. Tu choisis ? Raphaël choisit le train en bois. Les roues sont lisses. Ils font un rail. Le bois claque un peu. Le train glisse. Il glisse. Oui. Tout doucement. On ajoute un wagon ? Raphaël pose un wagon rouge. Le wagon fait clic. Clic. Bravo. Ils ajoutent un pont. Le pont est petit et jaune. Le train passe dessous. Sous le pont. Oui. Sous le pont. Bravo. L'écran est éteint. Oui. Un autre jeu, c'est bien. Papa tape dans ses mains. Raphaël rit. La lampe orange veille encore.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Florian est dans sa chambre. Il regarde un petit écran. Des oiseaux passent. Papa s'assoit près du tapis. Papa dit : fini. L'adulte dit fini. Florian écoute. Parce que papa a dit fini, Florian va &lt;emphasis level="moderate"&gt;éteindre&lt;/emphasis&gt;. Florian éteint l'écran. L'écran devient noir. Il pose la tablette. Papa dit : on prend un autre jeu. Florian va choisir un jeu. Il choisit le train en bois. Les roues sont lisses. Ils font un rail. Le train glisse. Florian dit : l'écran est éteint. Un autre jeu, c'est bien. Papa tape dans ses mains. Florian rit. Ils ajoutent un pont. Puis ils rangent les rails. Florian a su éteindre. Il a choisi un autre jeu.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une petite lampe orange veille. Elle est près du lit. Le plancher de bois craque un peu. Un doudou attend sur l'oreiller. Une boîte de train est dans le coin. Ça sent le bois et le linge. Un rail dépasse déjà de la boîte. La fenêtre est un peu embuée. Raphaël, je m'assois ici. Tu vois la lampe ? Oui, papa. Elle est orange. En ce moment, Raphaël tient la tablette. Des oiseaux passent sur l'écran. Leurs ailes sont bleues. Les oiseaux, papa. Oui. Ils passent. Papa s'assoit près du tapis. Le tapis est un peu rêche. Fini. L'adulte dit fini. Raphaël écoute. C'est fini. On va éteindre. Raphaël va éteindre. Raphaël éteint l'écran. L'écran devient noir. Il pose la tablette. Bravo, Raphaël. Tu as éteint. On prend un autre jeu. Un autre jeu. Tu choisis ? Raphaël choisit le train en bois. Les roues sont lisses. Ils font un rail. Le bois claque un peu. Le train glisse. Il glisse. Oui. Tout doucement. On ajoute un wagon ? Raphaël pose un wagon rouge. Le wagon fait clic. Clic. Bravo. Ils ajoutent un pont. Le pont est petit et jaune. Le train passe dessous. Sous le pont. Oui. Sous le pont. Bravo. L'écran est éteint. Oui. Un autre jeu, c'est bien. Papa tape dans ses mains. Raphaël rit. La lampe orange veille encore.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1378,7 +1378,6 @@
 papa|Oui.
 papa|Sous le pont.
 papa|Bravo.
-papa|Tu as fait du bon travail.
 enfant-m|L'écran est éteint.
 papa|Oui.
 papa|Un autre jeu, c'est bien.
@@ -1421,7 +1420,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Papa dit fini. Que fait Florian ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa dit fini. Que fait Raphaël ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1576,7 +1575,6 @@
 narrateur|Que fait Raphaël ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1606,7 +1604,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa a dit fini. Florian a éteint. Il a pris un &lt;emphasis level="moderate"&gt;autre&lt;/emphasis&gt; jeu. Le train en bois, c'était bien.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa a dit fini. L'adulte a dit fini. Raphaël a éteint. Il a pris un autre jeu. Tu as éteint l'écran ? Oui, papa. Et après ? Un autre jeu. Bravo. Le train en bois, c'était bien. Raphaël touche une roue. La roue est lisse. Le wagon est encore dessus ? Oui, papa. Le pont jaune reste en place. La lampe veille encore.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1763,7 +1761,6 @@
 narrateur|La lampe veille encore.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1793,7 +1790,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le train reste sur le pont. Florian dit merci à papa. La chambre est calme.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le train reste sur le pont. On range les rails ? Ils rangent les rails. Le bois claque, tout doucement. Tu as fini de ranger ? Oui, papa. Bravo. Merci, papa. Merci, Raphaël. On pose le doudou ? Raphaël pose le doudou. Le doudou attend encore. La chambre est calme.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1939,7 +1936,6 @@
 narrateur|La chambre est calme.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1964,12 +1960,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le train reste sur le pont. L'écran est éteint. Oui. Bravo, Raphaël. L'histoire est finie.</t>
+          <t>Le train reste sur le pont. L'écran est éteint. Oui. Bravo, Raphaël.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le train reste sur le pont. L'écran est éteint. Oui. Bravo, Raphaël.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2107,11 +2103,9 @@
           <t>narrateur|Le train reste sur le pont.
 enfant-m|L'écran est éteint.
 papa|Oui.
-papa|Bravo, Raphaël.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+papa|Bravo, Raphaël.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2130,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2175,6 +2169,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ECR.001-09.xlsx
+++ b/stories/arbres/ATOM-SAN.ECR.001-09.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>chambre</t>
+          <t>chambre, lampe orange, train en bois</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Florian, papa</t>
+          <t>Raphaël, papa</t>
         </is>
       </c>
     </row>
